--- a/data/spiff_rebates.xlsx
+++ b/data/spiff_rebates.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Python\Practice\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7920A40E-231B-40B0-AC61-C5D8B4A2A954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D37C5E1-9A96-4DAB-AB25-7FB8B372955C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{20A5ED59-561A-49C7-A642-2BE13030F89B}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1901" uniqueCount="183">
   <si>
     <t>Exp Comm</t>
   </si>
@@ -517,6 +517,81 @@
   </si>
   <si>
     <t>Quikcell 32W POWER DELIVERY Dual Port Wall Charger - Black</t>
+  </si>
+  <si>
+    <t>joel aguilar</t>
+  </si>
+  <si>
+    <t>Quikcell Samsung Galaxy A16 5G Grand ADVOCATE Dual-Layer Kickstand Case Armor Black</t>
+  </si>
+  <si>
+    <t>Angel Juarez</t>
+  </si>
+  <si>
+    <t>regina salazar</t>
+  </si>
+  <si>
+    <t>Credit Card; Debit Card</t>
+  </si>
+  <si>
+    <t>jennifer  laws</t>
+  </si>
+  <si>
+    <t>Speck Moto g 5G SHIELDVIEW Premium Glass + Applicator</t>
+  </si>
+  <si>
+    <t>farrar rickey</t>
+  </si>
+  <si>
+    <t>teodora martinez</t>
+  </si>
+  <si>
+    <t>vermonica gaddy</t>
+  </si>
+  <si>
+    <t>Quikcell Samsung Galaxy A17 5G Ultra OPERATOR Rugged Protective Case – Energy Pink</t>
+  </si>
+  <si>
+    <t>jose moronta</t>
+  </si>
+  <si>
+    <t>Quikcell Samsung Galaxy A16 5G Grand ADVOCATE Dual-Layer Kickstand Case Navy Blue</t>
+  </si>
+  <si>
+    <t>jacob auman</t>
+  </si>
+  <si>
+    <t>jeffery brisson</t>
+  </si>
+  <si>
+    <t>Quikcell Moto g 5G OPERATOR Rugged Protective Case Armor Black</t>
+  </si>
+  <si>
+    <t>malek jones</t>
+  </si>
+  <si>
+    <t>Quikcell QAIR BUDS 100 - White</t>
+  </si>
+  <si>
+    <t>ramirez ramirez</t>
+  </si>
+  <si>
+    <t>wright wright</t>
+  </si>
+  <si>
+    <t>fuller Christal</t>
+  </si>
+  <si>
+    <t>Patricia Ingold-Wright</t>
+  </si>
+  <si>
+    <t>Buchanan Buchanan</t>
+  </si>
+  <si>
+    <t>franklin franklin</t>
+  </si>
+  <si>
+    <t>grace grace</t>
   </si>
 </sst>
 </file>
@@ -8769,7 +8844,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DF99710-49B8-4B87-9581-744E8342F589}">
-  <dimension ref="A1:W119"/>
+  <dimension ref="A1:W161"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.109375" bestFit="1" customWidth="1"/>
@@ -15881,6 +15956,2499 @@
         <v>81</v>
       </c>
     </row>
+    <row r="120" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>31</v>
+      </c>
+      <c r="B120">
+        <v>46217.629143518519</v>
+      </c>
+      <c r="C120" t="s">
+        <v>88</v>
+      </c>
+      <c r="D120" t="s">
+        <v>158</v>
+      </c>
+      <c r="F120" t="s">
+        <v>77</v>
+      </c>
+      <c r="G120" t="s">
+        <v>157</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q120">
+        <v>0</v>
+      </c>
+      <c r="R120" t="s">
+        <v>80</v>
+      </c>
+      <c r="U120">
+        <v>846537077012</v>
+      </c>
+      <c r="V120">
+        <v>169271</v>
+      </c>
+      <c r="W120" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>31</v>
+      </c>
+      <c r="B121">
+        <v>46217.643287037034</v>
+      </c>
+      <c r="C121" t="s">
+        <v>88</v>
+      </c>
+      <c r="D121" t="s">
+        <v>158</v>
+      </c>
+      <c r="F121" t="s">
+        <v>77</v>
+      </c>
+      <c r="G121" t="s">
+        <v>157</v>
+      </c>
+      <c r="H121">
+        <v>1</v>
+      </c>
+      <c r="I121">
+        <v>25</v>
+      </c>
+      <c r="J121">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="K121">
+        <v>0</v>
+      </c>
+      <c r="L121">
+        <v>25</v>
+      </c>
+      <c r="M121">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="N121">
+        <v>16.21</v>
+      </c>
+      <c r="O121">
+        <v>0</v>
+      </c>
+      <c r="P121" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q121">
+        <v>25</v>
+      </c>
+      <c r="U121">
+        <v>846537077012</v>
+      </c>
+      <c r="V121">
+        <v>169271</v>
+      </c>
+      <c r="W121" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>31</v>
+      </c>
+      <c r="B122">
+        <v>46217.643287037034</v>
+      </c>
+      <c r="C122" t="s">
+        <v>88</v>
+      </c>
+      <c r="D122" t="s">
+        <v>158</v>
+      </c>
+      <c r="F122" t="s">
+        <v>77</v>
+      </c>
+      <c r="G122" t="s">
+        <v>159</v>
+      </c>
+      <c r="H122">
+        <v>1</v>
+      </c>
+      <c r="I122">
+        <v>12</v>
+      </c>
+      <c r="J122">
+        <v>5.27</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>12</v>
+      </c>
+      <c r="M122">
+        <v>5.27</v>
+      </c>
+      <c r="N122">
+        <v>6.73</v>
+      </c>
+      <c r="O122">
+        <v>0</v>
+      </c>
+      <c r="P122" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q122">
+        <v>12</v>
+      </c>
+      <c r="U122">
+        <v>846537094460</v>
+      </c>
+      <c r="V122">
+        <v>169271</v>
+      </c>
+      <c r="W122" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>31</v>
+      </c>
+      <c r="B123">
+        <v>46219.443969907406</v>
+      </c>
+      <c r="C123" t="s">
+        <v>88</v>
+      </c>
+      <c r="D123" t="s">
+        <v>160</v>
+      </c>
+      <c r="F123" t="s">
+        <v>77</v>
+      </c>
+      <c r="G123" t="s">
+        <v>118</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
+      </c>
+      <c r="P123" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q123">
+        <v>0</v>
+      </c>
+      <c r="R123" t="s">
+        <v>80</v>
+      </c>
+      <c r="U123">
+        <v>738516585857</v>
+      </c>
+      <c r="V123">
+        <v>169271</v>
+      </c>
+      <c r="W123" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>31</v>
+      </c>
+      <c r="B124">
+        <v>46219.443969907406</v>
+      </c>
+      <c r="C124" t="s">
+        <v>88</v>
+      </c>
+      <c r="D124" t="s">
+        <v>160</v>
+      </c>
+      <c r="F124" t="s">
+        <v>77</v>
+      </c>
+      <c r="G124" t="s">
+        <v>82</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>0</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q124">
+        <v>0</v>
+      </c>
+      <c r="R124" t="s">
+        <v>80</v>
+      </c>
+      <c r="U124">
+        <v>846537095665</v>
+      </c>
+      <c r="V124">
+        <v>169271</v>
+      </c>
+      <c r="W124" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>31</v>
+      </c>
+      <c r="B125">
+        <v>46219.493368055555</v>
+      </c>
+      <c r="C125" t="s">
+        <v>88</v>
+      </c>
+      <c r="D125" t="s">
+        <v>161</v>
+      </c>
+      <c r="F125" t="s">
+        <v>77</v>
+      </c>
+      <c r="G125" t="s">
+        <v>157</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>0</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="N125">
+        <v>0</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q125">
+        <v>0</v>
+      </c>
+      <c r="R125" t="s">
+        <v>80</v>
+      </c>
+      <c r="U125">
+        <v>846537077012</v>
+      </c>
+      <c r="V125">
+        <v>169271</v>
+      </c>
+      <c r="W125" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>31</v>
+      </c>
+      <c r="B126">
+        <v>46219.495289351849</v>
+      </c>
+      <c r="C126" t="s">
+        <v>88</v>
+      </c>
+      <c r="D126" t="s">
+        <v>161</v>
+      </c>
+      <c r="F126" t="s">
+        <v>77</v>
+      </c>
+      <c r="G126" t="s">
+        <v>157</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+      <c r="N126">
+        <v>0</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q126">
+        <v>0</v>
+      </c>
+      <c r="R126" t="s">
+        <v>80</v>
+      </c>
+      <c r="U126">
+        <v>846537077012</v>
+      </c>
+      <c r="V126">
+        <v>169271</v>
+      </c>
+      <c r="W126" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="127" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>31</v>
+      </c>
+      <c r="B127">
+        <v>46219.496782407405</v>
+      </c>
+      <c r="C127" t="s">
+        <v>88</v>
+      </c>
+      <c r="D127" t="s">
+        <v>161</v>
+      </c>
+      <c r="F127" t="s">
+        <v>77</v>
+      </c>
+      <c r="G127" t="s">
+        <v>157</v>
+      </c>
+      <c r="H127">
+        <v>1</v>
+      </c>
+      <c r="I127">
+        <v>32</v>
+      </c>
+      <c r="J127">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>32</v>
+      </c>
+      <c r="M127">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="N127">
+        <v>23.21</v>
+      </c>
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q127">
+        <v>32</v>
+      </c>
+      <c r="U127">
+        <v>846537077012</v>
+      </c>
+      <c r="V127">
+        <v>169271</v>
+      </c>
+      <c r="W127" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="128" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>31</v>
+      </c>
+      <c r="B128">
+        <v>46219.634212962963</v>
+      </c>
+      <c r="C128" t="s">
+        <v>88</v>
+      </c>
+      <c r="D128" t="s">
+        <v>163</v>
+      </c>
+      <c r="F128" t="s">
+        <v>77</v>
+      </c>
+      <c r="G128" t="s">
+        <v>157</v>
+      </c>
+      <c r="H128">
+        <v>1</v>
+      </c>
+      <c r="I128">
+        <v>33</v>
+      </c>
+      <c r="J128">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>33</v>
+      </c>
+      <c r="M128">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="N128">
+        <v>24.21</v>
+      </c>
+      <c r="O128">
+        <v>0</v>
+      </c>
+      <c r="P128" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q128">
+        <v>33</v>
+      </c>
+      <c r="U128">
+        <v>846537077012</v>
+      </c>
+      <c r="V128">
+        <v>169271</v>
+      </c>
+      <c r="W128" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="129" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>31</v>
+      </c>
+      <c r="B129">
+        <v>46219.634212962963</v>
+      </c>
+      <c r="C129" t="s">
+        <v>88</v>
+      </c>
+      <c r="D129" t="s">
+        <v>163</v>
+      </c>
+      <c r="F129" t="s">
+        <v>77</v>
+      </c>
+      <c r="G129" t="s">
+        <v>164</v>
+      </c>
+      <c r="H129">
+        <v>1</v>
+      </c>
+      <c r="I129">
+        <v>47</v>
+      </c>
+      <c r="J129">
+        <v>7.39</v>
+      </c>
+      <c r="K129">
+        <v>0</v>
+      </c>
+      <c r="L129">
+        <v>47</v>
+      </c>
+      <c r="M129">
+        <v>7.39</v>
+      </c>
+      <c r="N129">
+        <v>39.61</v>
+      </c>
+      <c r="O129">
+        <v>0</v>
+      </c>
+      <c r="P129" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q129">
+        <v>47</v>
+      </c>
+      <c r="U129">
+        <v>840168519286</v>
+      </c>
+      <c r="V129">
+        <v>169271</v>
+      </c>
+      <c r="W129" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="130" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>31</v>
+      </c>
+      <c r="B130">
+        <v>46219.689826388887</v>
+      </c>
+      <c r="C130" t="s">
+        <v>88</v>
+      </c>
+      <c r="D130" t="s">
+        <v>165</v>
+      </c>
+      <c r="F130" t="s">
+        <v>77</v>
+      </c>
+      <c r="G130" t="s">
+        <v>118</v>
+      </c>
+      <c r="H130">
+        <v>1</v>
+      </c>
+      <c r="I130">
+        <v>27.01</v>
+      </c>
+      <c r="J130">
+        <v>7.69</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>27.01</v>
+      </c>
+      <c r="M130">
+        <v>7.69</v>
+      </c>
+      <c r="N130">
+        <v>19.32</v>
+      </c>
+      <c r="O130">
+        <v>0</v>
+      </c>
+      <c r="P130" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q130">
+        <v>27.01</v>
+      </c>
+      <c r="U130">
+        <v>738516585857</v>
+      </c>
+      <c r="V130">
+        <v>169271</v>
+      </c>
+      <c r="W130" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="131" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>31</v>
+      </c>
+      <c r="B131">
+        <v>46219.757141203707</v>
+      </c>
+      <c r="C131" t="s">
+        <v>75</v>
+      </c>
+      <c r="D131" t="s">
+        <v>166</v>
+      </c>
+      <c r="F131" t="s">
+        <v>77</v>
+      </c>
+      <c r="G131" t="s">
+        <v>157</v>
+      </c>
+      <c r="H131">
+        <v>1</v>
+      </c>
+      <c r="I131">
+        <v>34.99</v>
+      </c>
+      <c r="J131">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>34.99</v>
+      </c>
+      <c r="M131">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="N131">
+        <v>26.2</v>
+      </c>
+      <c r="O131">
+        <v>0</v>
+      </c>
+      <c r="P131" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q131">
+        <v>34.99</v>
+      </c>
+      <c r="U131">
+        <v>846537077012</v>
+      </c>
+      <c r="V131">
+        <v>169271</v>
+      </c>
+      <c r="W131" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="132" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>31</v>
+      </c>
+      <c r="B132">
+        <v>46220.504837962966</v>
+      </c>
+      <c r="C132" t="s">
+        <v>75</v>
+      </c>
+      <c r="D132" t="s">
+        <v>160</v>
+      </c>
+      <c r="F132" t="s">
+        <v>77</v>
+      </c>
+      <c r="G132" t="s">
+        <v>157</v>
+      </c>
+      <c r="H132">
+        <v>3</v>
+      </c>
+      <c r="I132">
+        <v>25.3</v>
+      </c>
+      <c r="J132">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="M132">
+        <v>26.37</v>
+      </c>
+      <c r="N132">
+        <v>49.53</v>
+      </c>
+      <c r="O132">
+        <v>0</v>
+      </c>
+      <c r="P132" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q132">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="U132">
+        <v>846537077012</v>
+      </c>
+      <c r="V132">
+        <v>169271</v>
+      </c>
+      <c r="W132" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="133" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>31</v>
+      </c>
+      <c r="B133">
+        <v>46220.692488425928</v>
+      </c>
+      <c r="C133" t="s">
+        <v>75</v>
+      </c>
+      <c r="D133" t="s">
+        <v>167</v>
+      </c>
+      <c r="F133" t="s">
+        <v>77</v>
+      </c>
+      <c r="G133" t="s">
+        <v>157</v>
+      </c>
+      <c r="H133">
+        <v>1</v>
+      </c>
+      <c r="I133">
+        <v>30.02</v>
+      </c>
+      <c r="J133">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>30.02</v>
+      </c>
+      <c r="M133">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="N133">
+        <v>21.23</v>
+      </c>
+      <c r="O133">
+        <v>0</v>
+      </c>
+      <c r="P133" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q133">
+        <v>30.02</v>
+      </c>
+      <c r="U133">
+        <v>846537077012</v>
+      </c>
+      <c r="V133">
+        <v>169271</v>
+      </c>
+      <c r="W133" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="134" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>31</v>
+      </c>
+      <c r="B134">
+        <v>46220.692488425928</v>
+      </c>
+      <c r="C134" t="s">
+        <v>75</v>
+      </c>
+      <c r="D134" t="s">
+        <v>167</v>
+      </c>
+      <c r="F134" t="s">
+        <v>77</v>
+      </c>
+      <c r="G134" t="s">
+        <v>168</v>
+      </c>
+      <c r="H134">
+        <v>1</v>
+      </c>
+      <c r="I134">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="J134">
+        <v>4.71</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="M134">
+        <v>4.71</v>
+      </c>
+      <c r="N134">
+        <v>15.28</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q134">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="U134">
+        <v>846537098062</v>
+      </c>
+      <c r="V134">
+        <v>169271</v>
+      </c>
+      <c r="W134" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="135" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>31</v>
+      </c>
+      <c r="B135">
+        <v>46221.558634259258</v>
+      </c>
+      <c r="C135" t="s">
+        <v>75</v>
+      </c>
+      <c r="D135" t="s">
+        <v>92</v>
+      </c>
+      <c r="F135" t="s">
+        <v>77</v>
+      </c>
+      <c r="G135" t="s">
+        <v>101</v>
+      </c>
+      <c r="H135">
+        <v>1</v>
+      </c>
+      <c r="I135">
+        <v>24.99</v>
+      </c>
+      <c r="J135">
+        <v>2.96</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>24.99</v>
+      </c>
+      <c r="M135">
+        <v>2.96</v>
+      </c>
+      <c r="N135">
+        <v>22.03</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q135">
+        <v>24.99</v>
+      </c>
+      <c r="U135">
+        <v>846537094521</v>
+      </c>
+      <c r="V135">
+        <v>169271</v>
+      </c>
+      <c r="W135" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="136" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>31</v>
+      </c>
+      <c r="B136">
+        <v>46221.558634259258</v>
+      </c>
+      <c r="C136" t="s">
+        <v>75</v>
+      </c>
+      <c r="D136" t="s">
+        <v>92</v>
+      </c>
+      <c r="F136" t="s">
+        <v>77</v>
+      </c>
+      <c r="G136" t="s">
+        <v>159</v>
+      </c>
+      <c r="H136">
+        <v>1</v>
+      </c>
+      <c r="I136">
+        <v>29.99</v>
+      </c>
+      <c r="J136">
+        <v>5.27</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>29.99</v>
+      </c>
+      <c r="M136">
+        <v>5.27</v>
+      </c>
+      <c r="N136">
+        <v>24.72</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+      <c r="P136" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q136">
+        <v>29.99</v>
+      </c>
+      <c r="U136">
+        <v>846537094460</v>
+      </c>
+      <c r="V136">
+        <v>169271</v>
+      </c>
+      <c r="W136" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="137" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>31</v>
+      </c>
+      <c r="B137">
+        <v>46221.611203703702</v>
+      </c>
+      <c r="C137" t="s">
+        <v>75</v>
+      </c>
+      <c r="D137" t="s">
+        <v>169</v>
+      </c>
+      <c r="F137" t="s">
+        <v>77</v>
+      </c>
+      <c r="G137" t="s">
+        <v>159</v>
+      </c>
+      <c r="H137">
+        <v>1</v>
+      </c>
+      <c r="I137">
+        <v>29.99</v>
+      </c>
+      <c r="J137">
+        <v>5.27</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>29.99</v>
+      </c>
+      <c r="M137">
+        <v>5.27</v>
+      </c>
+      <c r="N137">
+        <v>24.72</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q137">
+        <v>29.99</v>
+      </c>
+      <c r="U137">
+        <v>846537094460</v>
+      </c>
+      <c r="V137">
+        <v>169271</v>
+      </c>
+      <c r="W137" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="138" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>31</v>
+      </c>
+      <c r="B138">
+        <v>46221.611203703702</v>
+      </c>
+      <c r="C138" t="s">
+        <v>75</v>
+      </c>
+      <c r="D138" t="s">
+        <v>169</v>
+      </c>
+      <c r="F138" t="s">
+        <v>77</v>
+      </c>
+      <c r="G138" t="s">
+        <v>170</v>
+      </c>
+      <c r="H138">
+        <v>1</v>
+      </c>
+      <c r="I138">
+        <v>29.99</v>
+      </c>
+      <c r="J138">
+        <v>5.27</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>29.99</v>
+      </c>
+      <c r="M138">
+        <v>5.27</v>
+      </c>
+      <c r="N138">
+        <v>24.72</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q138">
+        <v>29.99</v>
+      </c>
+      <c r="U138">
+        <v>846537094477</v>
+      </c>
+      <c r="V138">
+        <v>169271</v>
+      </c>
+      <c r="W138" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="139" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>31</v>
+      </c>
+      <c r="B139">
+        <v>46221.611203703702</v>
+      </c>
+      <c r="C139" t="s">
+        <v>75</v>
+      </c>
+      <c r="D139" t="s">
+        <v>169</v>
+      </c>
+      <c r="F139" t="s">
+        <v>77</v>
+      </c>
+      <c r="G139" t="s">
+        <v>157</v>
+      </c>
+      <c r="H139">
+        <v>1</v>
+      </c>
+      <c r="I139">
+        <v>25.02</v>
+      </c>
+      <c r="J139">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>25.02</v>
+      </c>
+      <c r="M139">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="N139">
+        <v>16.23</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q139">
+        <v>25.02</v>
+      </c>
+      <c r="U139">
+        <v>846537077012</v>
+      </c>
+      <c r="V139">
+        <v>169271</v>
+      </c>
+      <c r="W139" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="140" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>31</v>
+      </c>
+      <c r="B140">
+        <v>46223.655162037037</v>
+      </c>
+      <c r="C140" t="s">
+        <v>75</v>
+      </c>
+      <c r="D140" t="s">
+        <v>171</v>
+      </c>
+      <c r="F140" t="s">
+        <v>77</v>
+      </c>
+      <c r="G140" t="s">
+        <v>164</v>
+      </c>
+      <c r="H140">
+        <v>1</v>
+      </c>
+      <c r="I140">
+        <v>35</v>
+      </c>
+      <c r="J140">
+        <v>7.39</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>35</v>
+      </c>
+      <c r="M140">
+        <v>7.39</v>
+      </c>
+      <c r="N140">
+        <v>27.61</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q140">
+        <v>35</v>
+      </c>
+      <c r="U140">
+        <v>840168519286</v>
+      </c>
+      <c r="V140">
+        <v>169271</v>
+      </c>
+      <c r="W140" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="141" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>31</v>
+      </c>
+      <c r="B141">
+        <v>46223.677361111113</v>
+      </c>
+      <c r="C141" t="s">
+        <v>75</v>
+      </c>
+      <c r="D141" t="s">
+        <v>172</v>
+      </c>
+      <c r="F141" t="s">
+        <v>77</v>
+      </c>
+      <c r="G141" t="s">
+        <v>173</v>
+      </c>
+      <c r="H141">
+        <v>1</v>
+      </c>
+      <c r="I141">
+        <v>12</v>
+      </c>
+      <c r="J141">
+        <v>3.29</v>
+      </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
+      <c r="L141">
+        <v>12</v>
+      </c>
+      <c r="M141">
+        <v>3.29</v>
+      </c>
+      <c r="N141">
+        <v>8.7100000000000009</v>
+      </c>
+      <c r="O141">
+        <v>0</v>
+      </c>
+      <c r="P141" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q141">
+        <v>12</v>
+      </c>
+      <c r="U141">
+        <v>846537085703</v>
+      </c>
+      <c r="V141">
+        <v>169271</v>
+      </c>
+      <c r="W141" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="142" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>31</v>
+      </c>
+      <c r="B142">
+        <v>46225.609571759262</v>
+      </c>
+      <c r="C142" t="s">
+        <v>75</v>
+      </c>
+      <c r="D142" t="s">
+        <v>174</v>
+      </c>
+      <c r="F142" t="s">
+        <v>77</v>
+      </c>
+      <c r="G142" t="s">
+        <v>175</v>
+      </c>
+      <c r="H142">
+        <v>1</v>
+      </c>
+      <c r="I142">
+        <v>39.99</v>
+      </c>
+      <c r="J142">
+        <v>21.99</v>
+      </c>
+      <c r="K142">
+        <v>0</v>
+      </c>
+      <c r="L142">
+        <v>39.99</v>
+      </c>
+      <c r="M142">
+        <v>21.99</v>
+      </c>
+      <c r="N142">
+        <v>18</v>
+      </c>
+      <c r="O142">
+        <v>0</v>
+      </c>
+      <c r="P142" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q142">
+        <v>39.99</v>
+      </c>
+      <c r="U142">
+        <v>846537096969</v>
+      </c>
+      <c r="V142">
+        <v>169271</v>
+      </c>
+      <c r="W142" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="143" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>31</v>
+      </c>
+      <c r="B143">
+        <v>46225.609571759262</v>
+      </c>
+      <c r="C143" t="s">
+        <v>75</v>
+      </c>
+      <c r="D143" t="s">
+        <v>174</v>
+      </c>
+      <c r="F143" t="s">
+        <v>77</v>
+      </c>
+      <c r="G143" t="s">
+        <v>82</v>
+      </c>
+      <c r="H143">
+        <v>1</v>
+      </c>
+      <c r="I143">
+        <v>23.02</v>
+      </c>
+      <c r="J143">
+        <v>2.96</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="L143">
+        <v>23.02</v>
+      </c>
+      <c r="M143">
+        <v>2.96</v>
+      </c>
+      <c r="N143">
+        <v>20.059999999999999</v>
+      </c>
+      <c r="O143">
+        <v>0</v>
+      </c>
+      <c r="P143" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q143">
+        <v>23.02</v>
+      </c>
+      <c r="U143">
+        <v>846537095665</v>
+      </c>
+      <c r="V143">
+        <v>169271</v>
+      </c>
+      <c r="W143" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="144" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>31</v>
+      </c>
+      <c r="B144">
+        <v>46225.609571759262</v>
+      </c>
+      <c r="C144" t="s">
+        <v>75</v>
+      </c>
+      <c r="D144" t="s">
+        <v>174</v>
+      </c>
+      <c r="F144" t="s">
+        <v>77</v>
+      </c>
+      <c r="G144" t="s">
+        <v>118</v>
+      </c>
+      <c r="H144">
+        <v>1</v>
+      </c>
+      <c r="I144">
+        <v>29.99</v>
+      </c>
+      <c r="J144">
+        <v>7.69</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
+      <c r="L144">
+        <v>29.99</v>
+      </c>
+      <c r="M144">
+        <v>7.69</v>
+      </c>
+      <c r="N144">
+        <v>22.3</v>
+      </c>
+      <c r="O144">
+        <v>0</v>
+      </c>
+      <c r="P144" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q144">
+        <v>29.99</v>
+      </c>
+      <c r="U144">
+        <v>738516585857</v>
+      </c>
+      <c r="V144">
+        <v>169271</v>
+      </c>
+      <c r="W144" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="145" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>31</v>
+      </c>
+      <c r="B145">
+        <v>46226.677060185182</v>
+      </c>
+      <c r="C145" t="s">
+        <v>75</v>
+      </c>
+      <c r="D145" t="s">
+        <v>139</v>
+      </c>
+      <c r="F145" t="s">
+        <v>77</v>
+      </c>
+      <c r="G145" t="s">
+        <v>164</v>
+      </c>
+      <c r="H145">
+        <v>1</v>
+      </c>
+      <c r="I145">
+        <v>38</v>
+      </c>
+      <c r="J145">
+        <v>7.39</v>
+      </c>
+      <c r="K145">
+        <v>0</v>
+      </c>
+      <c r="L145">
+        <v>38</v>
+      </c>
+      <c r="M145">
+        <v>7.39</v>
+      </c>
+      <c r="N145">
+        <v>30.61</v>
+      </c>
+      <c r="O145">
+        <v>0</v>
+      </c>
+      <c r="P145" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q145">
+        <v>38</v>
+      </c>
+      <c r="U145">
+        <v>840168519286</v>
+      </c>
+      <c r="V145">
+        <v>169271</v>
+      </c>
+      <c r="W145" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="146" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>31</v>
+      </c>
+      <c r="B146">
+        <v>46229.427407407406</v>
+      </c>
+      <c r="C146" t="s">
+        <v>75</v>
+      </c>
+      <c r="D146" t="s">
+        <v>153</v>
+      </c>
+      <c r="F146" t="s">
+        <v>77</v>
+      </c>
+      <c r="G146" t="s">
+        <v>137</v>
+      </c>
+      <c r="H146">
+        <v>1</v>
+      </c>
+      <c r="I146">
+        <v>39.99</v>
+      </c>
+      <c r="J146">
+        <v>21.99</v>
+      </c>
+      <c r="K146">
+        <v>0</v>
+      </c>
+      <c r="L146">
+        <v>39.99</v>
+      </c>
+      <c r="M146">
+        <v>21.99</v>
+      </c>
+      <c r="N146">
+        <v>18</v>
+      </c>
+      <c r="O146">
+        <v>0</v>
+      </c>
+      <c r="P146" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q146">
+        <v>39.99</v>
+      </c>
+      <c r="U146">
+        <v>846537096952</v>
+      </c>
+      <c r="V146">
+        <v>169271</v>
+      </c>
+      <c r="W146" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="147" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>31</v>
+      </c>
+      <c r="B147">
+        <v>46229.555486111109</v>
+      </c>
+      <c r="C147" t="s">
+        <v>75</v>
+      </c>
+      <c r="D147" t="s">
+        <v>176</v>
+      </c>
+      <c r="F147" t="s">
+        <v>77</v>
+      </c>
+      <c r="G147" t="s">
+        <v>175</v>
+      </c>
+      <c r="H147">
+        <v>1</v>
+      </c>
+      <c r="I147">
+        <v>30.02</v>
+      </c>
+      <c r="J147">
+        <v>21.99</v>
+      </c>
+      <c r="K147">
+        <v>0</v>
+      </c>
+      <c r="L147">
+        <v>30.02</v>
+      </c>
+      <c r="M147">
+        <v>21.99</v>
+      </c>
+      <c r="N147">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="O147">
+        <v>0</v>
+      </c>
+      <c r="P147" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q147">
+        <v>30.02</v>
+      </c>
+      <c r="U147">
+        <v>846537096969</v>
+      </c>
+      <c r="V147">
+        <v>169271</v>
+      </c>
+      <c r="W147" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="148" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>31</v>
+      </c>
+      <c r="B148">
+        <v>46229.555486111109</v>
+      </c>
+      <c r="C148" t="s">
+        <v>75</v>
+      </c>
+      <c r="D148" t="s">
+        <v>176</v>
+      </c>
+      <c r="F148" t="s">
+        <v>77</v>
+      </c>
+      <c r="G148" t="s">
+        <v>89</v>
+      </c>
+      <c r="H148">
+        <v>1</v>
+      </c>
+      <c r="I148">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="J148">
+        <v>4.71</v>
+      </c>
+      <c r="K148">
+        <v>0</v>
+      </c>
+      <c r="L148">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="M148">
+        <v>4.71</v>
+      </c>
+      <c r="N148">
+        <v>15.28</v>
+      </c>
+      <c r="O148">
+        <v>0</v>
+      </c>
+      <c r="P148" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q148">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="U148">
+        <v>846537098048</v>
+      </c>
+      <c r="V148">
+        <v>169271</v>
+      </c>
+      <c r="W148" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="149" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>31</v>
+      </c>
+      <c r="B149">
+        <v>46229.555486111109</v>
+      </c>
+      <c r="C149" t="s">
+        <v>75</v>
+      </c>
+      <c r="D149" t="s">
+        <v>176</v>
+      </c>
+      <c r="F149" t="s">
+        <v>77</v>
+      </c>
+      <c r="G149" t="s">
+        <v>101</v>
+      </c>
+      <c r="H149">
+        <v>1</v>
+      </c>
+      <c r="I149">
+        <v>24.99</v>
+      </c>
+      <c r="J149">
+        <v>2.96</v>
+      </c>
+      <c r="K149">
+        <v>0</v>
+      </c>
+      <c r="L149">
+        <v>24.99</v>
+      </c>
+      <c r="M149">
+        <v>2.96</v>
+      </c>
+      <c r="N149">
+        <v>22.03</v>
+      </c>
+      <c r="O149">
+        <v>0</v>
+      </c>
+      <c r="P149" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q149">
+        <v>24.99</v>
+      </c>
+      <c r="U149">
+        <v>846537094521</v>
+      </c>
+      <c r="V149">
+        <v>169271</v>
+      </c>
+      <c r="W149" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="150" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>31</v>
+      </c>
+      <c r="B150">
+        <v>46230.528113425928</v>
+      </c>
+      <c r="C150" t="s">
+        <v>75</v>
+      </c>
+      <c r="D150" t="s">
+        <v>177</v>
+      </c>
+      <c r="F150" t="s">
+        <v>77</v>
+      </c>
+      <c r="G150" t="s">
+        <v>101</v>
+      </c>
+      <c r="H150">
+        <v>1</v>
+      </c>
+      <c r="I150">
+        <v>19</v>
+      </c>
+      <c r="J150">
+        <v>2.96</v>
+      </c>
+      <c r="K150">
+        <v>0</v>
+      </c>
+      <c r="L150">
+        <v>19</v>
+      </c>
+      <c r="M150">
+        <v>2.96</v>
+      </c>
+      <c r="N150">
+        <v>16.04</v>
+      </c>
+      <c r="O150">
+        <v>0</v>
+      </c>
+      <c r="P150" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q150">
+        <v>19</v>
+      </c>
+      <c r="U150">
+        <v>846537094521</v>
+      </c>
+      <c r="V150">
+        <v>169271</v>
+      </c>
+      <c r="W150" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="151" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>31</v>
+      </c>
+      <c r="B151">
+        <v>46230.543229166666</v>
+      </c>
+      <c r="C151" t="s">
+        <v>75</v>
+      </c>
+      <c r="D151" t="s">
+        <v>158</v>
+      </c>
+      <c r="F151" t="s">
+        <v>77</v>
+      </c>
+      <c r="G151" t="s">
+        <v>101</v>
+      </c>
+      <c r="H151">
+        <v>1</v>
+      </c>
+      <c r="I151">
+        <v>15</v>
+      </c>
+      <c r="J151">
+        <v>2.96</v>
+      </c>
+      <c r="K151">
+        <v>0</v>
+      </c>
+      <c r="L151">
+        <v>15</v>
+      </c>
+      <c r="M151">
+        <v>2.96</v>
+      </c>
+      <c r="N151">
+        <v>12.04</v>
+      </c>
+      <c r="O151">
+        <v>0</v>
+      </c>
+      <c r="P151" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q151">
+        <v>15</v>
+      </c>
+      <c r="U151">
+        <v>846537094521</v>
+      </c>
+      <c r="V151">
+        <v>169271</v>
+      </c>
+      <c r="W151" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="152" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>31</v>
+      </c>
+      <c r="B152">
+        <v>46231.794803240744</v>
+      </c>
+      <c r="C152" t="s">
+        <v>75</v>
+      </c>
+      <c r="D152" t="s">
+        <v>83</v>
+      </c>
+      <c r="F152" t="s">
+        <v>77</v>
+      </c>
+      <c r="G152" t="s">
+        <v>101</v>
+      </c>
+      <c r="H152">
+        <v>1</v>
+      </c>
+      <c r="I152">
+        <v>15.65</v>
+      </c>
+      <c r="J152">
+        <v>2.96</v>
+      </c>
+      <c r="K152">
+        <v>0</v>
+      </c>
+      <c r="L152">
+        <v>15.65</v>
+      </c>
+      <c r="M152">
+        <v>2.96</v>
+      </c>
+      <c r="N152">
+        <v>12.69</v>
+      </c>
+      <c r="O152">
+        <v>0</v>
+      </c>
+      <c r="P152" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q152">
+        <v>15.65</v>
+      </c>
+      <c r="U152">
+        <v>846537094521</v>
+      </c>
+      <c r="V152">
+        <v>169271</v>
+      </c>
+      <c r="W152" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="153" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>31</v>
+      </c>
+      <c r="B153">
+        <v>46232.562106481484</v>
+      </c>
+      <c r="C153" t="s">
+        <v>75</v>
+      </c>
+      <c r="D153" t="s">
+        <v>178</v>
+      </c>
+      <c r="F153" t="s">
+        <v>77</v>
+      </c>
+      <c r="G153" t="s">
+        <v>101</v>
+      </c>
+      <c r="H153">
+        <v>1</v>
+      </c>
+      <c r="I153">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="J153">
+        <v>2.96</v>
+      </c>
+      <c r="K153">
+        <v>0</v>
+      </c>
+      <c r="L153">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="M153">
+        <v>2.96</v>
+      </c>
+      <c r="N153">
+        <v>17.05</v>
+      </c>
+      <c r="O153">
+        <v>0</v>
+      </c>
+      <c r="P153" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q153">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="U153">
+        <v>846537094521</v>
+      </c>
+      <c r="V153">
+        <v>169271</v>
+      </c>
+      <c r="W153" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="154" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>31</v>
+      </c>
+      <c r="B154">
+        <v>46232.735578703701</v>
+      </c>
+      <c r="C154" t="s">
+        <v>75</v>
+      </c>
+      <c r="D154" t="s">
+        <v>179</v>
+      </c>
+      <c r="F154" t="s">
+        <v>77</v>
+      </c>
+      <c r="G154" t="s">
+        <v>101</v>
+      </c>
+      <c r="H154">
+        <v>1</v>
+      </c>
+      <c r="I154">
+        <v>24.99</v>
+      </c>
+      <c r="J154">
+        <v>2.96</v>
+      </c>
+      <c r="K154">
+        <v>0</v>
+      </c>
+      <c r="L154">
+        <v>24.99</v>
+      </c>
+      <c r="M154">
+        <v>2.96</v>
+      </c>
+      <c r="N154">
+        <v>22.03</v>
+      </c>
+      <c r="O154">
+        <v>0</v>
+      </c>
+      <c r="P154" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q154">
+        <v>24.99</v>
+      </c>
+      <c r="U154">
+        <v>846537094521</v>
+      </c>
+      <c r="V154">
+        <v>169271</v>
+      </c>
+      <c r="W154" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="155" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>31</v>
+      </c>
+      <c r="B155">
+        <v>46233.714444444442</v>
+      </c>
+      <c r="C155" t="s">
+        <v>75</v>
+      </c>
+      <c r="D155" t="s">
+        <v>180</v>
+      </c>
+      <c r="F155" t="s">
+        <v>77</v>
+      </c>
+      <c r="G155" t="s">
+        <v>170</v>
+      </c>
+      <c r="H155">
+        <v>1</v>
+      </c>
+      <c r="I155">
+        <v>25</v>
+      </c>
+      <c r="J155">
+        <v>5.27</v>
+      </c>
+      <c r="K155">
+        <v>0</v>
+      </c>
+      <c r="L155">
+        <v>25</v>
+      </c>
+      <c r="M155">
+        <v>5.27</v>
+      </c>
+      <c r="N155">
+        <v>19.73</v>
+      </c>
+      <c r="O155">
+        <v>0</v>
+      </c>
+      <c r="P155" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q155">
+        <v>25</v>
+      </c>
+      <c r="U155">
+        <v>846537094477</v>
+      </c>
+      <c r="V155">
+        <v>169271</v>
+      </c>
+      <c r="W155" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="156" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>31</v>
+      </c>
+      <c r="B156">
+        <v>46233.714444444442</v>
+      </c>
+      <c r="C156" t="s">
+        <v>75</v>
+      </c>
+      <c r="D156" t="s">
+        <v>180</v>
+      </c>
+      <c r="F156" t="s">
+        <v>77</v>
+      </c>
+      <c r="G156" t="s">
+        <v>101</v>
+      </c>
+      <c r="H156">
+        <v>1</v>
+      </c>
+      <c r="I156">
+        <v>24.99</v>
+      </c>
+      <c r="J156">
+        <v>2.96</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <v>24.99</v>
+      </c>
+      <c r="M156">
+        <v>2.96</v>
+      </c>
+      <c r="N156">
+        <v>22.03</v>
+      </c>
+      <c r="O156">
+        <v>0</v>
+      </c>
+      <c r="P156" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q156">
+        <v>24.99</v>
+      </c>
+      <c r="U156">
+        <v>846537094521</v>
+      </c>
+      <c r="V156">
+        <v>169271</v>
+      </c>
+      <c r="W156" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="157" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>31</v>
+      </c>
+      <c r="B157">
+        <v>46233.714444444442</v>
+      </c>
+      <c r="C157" t="s">
+        <v>75</v>
+      </c>
+      <c r="D157" t="s">
+        <v>180</v>
+      </c>
+      <c r="F157" t="s">
+        <v>77</v>
+      </c>
+      <c r="G157" t="s">
+        <v>108</v>
+      </c>
+      <c r="H157">
+        <v>1</v>
+      </c>
+      <c r="I157">
+        <v>27.01</v>
+      </c>
+      <c r="J157">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>27.01</v>
+      </c>
+      <c r="M157">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="N157">
+        <v>18.22</v>
+      </c>
+      <c r="O157">
+        <v>0</v>
+      </c>
+      <c r="P157" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q157">
+        <v>27.01</v>
+      </c>
+      <c r="U157">
+        <v>846537082740</v>
+      </c>
+      <c r="V157">
+        <v>169271</v>
+      </c>
+      <c r="W157" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="158" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>31</v>
+      </c>
+      <c r="B158">
+        <v>46234.45815972222</v>
+      </c>
+      <c r="C158" t="s">
+        <v>75</v>
+      </c>
+      <c r="D158" t="s">
+        <v>181</v>
+      </c>
+      <c r="F158" t="s">
+        <v>77</v>
+      </c>
+      <c r="G158" t="s">
+        <v>159</v>
+      </c>
+      <c r="H158">
+        <v>1</v>
+      </c>
+      <c r="I158">
+        <v>21</v>
+      </c>
+      <c r="J158">
+        <v>5.27</v>
+      </c>
+      <c r="K158">
+        <v>0</v>
+      </c>
+      <c r="L158">
+        <v>21</v>
+      </c>
+      <c r="M158">
+        <v>5.27</v>
+      </c>
+      <c r="N158">
+        <v>15.73</v>
+      </c>
+      <c r="O158">
+        <v>1.58</v>
+      </c>
+      <c r="P158" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q158">
+        <v>22.58</v>
+      </c>
+      <c r="U158">
+        <v>846537094460</v>
+      </c>
+      <c r="V158">
+        <v>169271</v>
+      </c>
+      <c r="W158" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="159" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>31</v>
+      </c>
+      <c r="B159">
+        <v>46234.494293981479</v>
+      </c>
+      <c r="C159" t="s">
+        <v>75</v>
+      </c>
+      <c r="D159" t="s">
+        <v>83</v>
+      </c>
+      <c r="F159" t="s">
+        <v>77</v>
+      </c>
+      <c r="G159" t="s">
+        <v>173</v>
+      </c>
+      <c r="H159">
+        <v>1</v>
+      </c>
+      <c r="I159">
+        <v>10</v>
+      </c>
+      <c r="J159">
+        <v>3.29</v>
+      </c>
+      <c r="K159">
+        <v>0</v>
+      </c>
+      <c r="L159">
+        <v>10</v>
+      </c>
+      <c r="M159">
+        <v>3.29</v>
+      </c>
+      <c r="N159">
+        <v>6.71</v>
+      </c>
+      <c r="O159">
+        <v>0</v>
+      </c>
+      <c r="P159" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q159">
+        <v>10</v>
+      </c>
+      <c r="U159">
+        <v>846537085703</v>
+      </c>
+      <c r="V159">
+        <v>169271</v>
+      </c>
+      <c r="W159" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="160" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>31</v>
+      </c>
+      <c r="B160">
+        <v>46234.726469907408</v>
+      </c>
+      <c r="C160" t="s">
+        <v>75</v>
+      </c>
+      <c r="D160" t="s">
+        <v>182</v>
+      </c>
+      <c r="F160" t="s">
+        <v>77</v>
+      </c>
+      <c r="G160" t="s">
+        <v>101</v>
+      </c>
+      <c r="H160">
+        <v>2</v>
+      </c>
+      <c r="I160">
+        <v>18.5</v>
+      </c>
+      <c r="J160">
+        <v>2.96</v>
+      </c>
+      <c r="K160">
+        <v>0</v>
+      </c>
+      <c r="L160">
+        <v>37</v>
+      </c>
+      <c r="M160">
+        <v>5.92</v>
+      </c>
+      <c r="N160">
+        <v>31.08</v>
+      </c>
+      <c r="O160">
+        <v>0</v>
+      </c>
+      <c r="P160" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q160">
+        <v>37</v>
+      </c>
+      <c r="U160">
+        <v>846537094521</v>
+      </c>
+      <c r="V160">
+        <v>169271</v>
+      </c>
+      <c r="W160" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="161" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>31</v>
+      </c>
+      <c r="B161">
+        <v>46234.760706018518</v>
+      </c>
+      <c r="C161" t="s">
+        <v>75</v>
+      </c>
+      <c r="D161" t="s">
+        <v>92</v>
+      </c>
+      <c r="F161" t="s">
+        <v>77</v>
+      </c>
+      <c r="G161" t="s">
+        <v>101</v>
+      </c>
+      <c r="H161">
+        <v>1</v>
+      </c>
+      <c r="I161">
+        <v>24.2</v>
+      </c>
+      <c r="J161">
+        <v>2.96</v>
+      </c>
+      <c r="K161">
+        <v>0</v>
+      </c>
+      <c r="L161">
+        <v>24.2</v>
+      </c>
+      <c r="M161">
+        <v>2.96</v>
+      </c>
+      <c r="N161">
+        <v>21.24</v>
+      </c>
+      <c r="O161">
+        <v>0</v>
+      </c>
+      <c r="P161" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q161">
+        <v>24.2</v>
+      </c>
+      <c r="U161">
+        <v>846537094521</v>
+      </c>
+      <c r="V161">
+        <v>169271</v>
+      </c>
+      <c r="W161" t="s">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
